--- a/data/trans_orig/IP3105-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP3105-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tomar yogures en 2007 (tasa de respuesta: 98,79%)</t>
+          <t>Menores según la frecuencia de tomar yogures o petit suises en 2007 (tasa de respuesta: 98,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>658</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>8830</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>528</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>6581</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>625</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8694</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13910</t>
+          <t>13543</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12966</t>
+          <t>13052</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>10358</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22085</t>
+          <t>22477</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16370</t>
+          <t>15917</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29658</t>
+          <t>29329</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18493</t>
+          <t>18188</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32136</t>
+          <t>32400</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38083</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57835</t>
+          <t>57099</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52424</t>
+          <t>52093</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67353</t>
+          <t>67128</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46492</t>
+          <t>46434</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60330</t>
+          <t>61641</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>103455</t>
+          <t>102526</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>124427</t>
+          <t>123799</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,1%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7669</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4244</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>4568</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>710</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>5991</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11568</t>
+          <t>11342</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14047</t>
+          <t>13847</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10882</t>
+          <t>9965</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22535</t>
+          <t>21756</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11428</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23297</t>
+          <t>23360</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19155</t>
+          <t>19170</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23069</t>
+          <t>22461</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38312</t>
+          <t>38169</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42456</t>
+          <t>42422</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56323</t>
+          <t>56280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51770</t>
+          <t>51459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64516</t>
+          <t>64408</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>99946</t>
+          <t>98610</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>117397</t>
+          <t>117369</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,26%</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>2734</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>17363</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>9629</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20362</t>
+          <t>21194</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12222</t>
+          <t>11978</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23769</t>
+          <t>23096</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17237</t>
+          <t>17007</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30310</t>
+          <t>30268</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32146</t>
+          <t>31651</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49605</t>
+          <t>49812</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33972</t>
+          <t>34072</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46213</t>
+          <t>46277</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51972</t>
+          <t>51850</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67708</t>
+          <t>67158</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90556</t>
+          <t>90594</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>109218</t>
+          <t>109658</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,36%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>5648</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>787</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11570</t>
+          <t>11182</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12331</t>
+          <t>12730</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20333</t>
+          <t>19818</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12618</t>
+          <t>12179</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25882</t>
+          <t>25233</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12996</t>
+          <t>13262</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25847</t>
+          <t>26413</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>28062</t>
+          <t>28638</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>47352</t>
+          <t>46608</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32285</t>
+          <t>31925</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50854</t>
+          <t>50402</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34219</t>
+          <t>33522</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52187</t>
+          <t>51980</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>70995</t>
+          <t>69601</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>95971</t>
+          <t>95362</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,47%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>111047</t>
+          <t>111398</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>132691</t>
+          <t>133029</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>105754</t>
+          <t>104108</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>125422</t>
+          <t>125130</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>222357</t>
+          <t>223889</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>252069</t>
+          <t>254577</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>68,0%</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>8190</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2358</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10191</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>728</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2545</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>10032</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13345</t>
+          <t>13790</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>7438</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17448</t>
+          <t>18069</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13920</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>28099</t>
+          <t>28128</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10619</t>
+          <t>10967</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22577</t>
+          <t>22822</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>15878</t>
+          <t>16378</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>29952</t>
+          <t>30177</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>29563</t>
+          <t>30312</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>47943</t>
+          <t>46991</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>63267</t>
+          <t>62634</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>77867</t>
+          <t>77381</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>68775</t>
+          <t>69109</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>85157</t>
+          <t>85169</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>135759</t>
+          <t>137060</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>158360</t>
+          <t>158401</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,03%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>685</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>609</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8953</t>
+          <t>9289</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10439</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5474</t>
+          <t>5489</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>15846</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>17718</t>
+          <t>18579</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8582</t>
+          <t>8708</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>19136</t>
+          <t>19433</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>19199</t>
+          <t>18371</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>34184</t>
+          <t>33860</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>9545</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>20302</t>
+          <t>19876</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>14927</t>
+          <t>15326</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>17136</t>
+          <t>16717</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>32263</t>
+          <t>31047</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>30431</t>
+          <t>30165</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>43795</t>
+          <t>43870</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>30451</t>
+          <t>30754</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>43083</t>
+          <t>43186</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>64497</t>
+          <t>64009</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>82853</t>
+          <t>82991</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,53%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>17867</t>
+          <t>18898</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>19596</t>
+          <t>18392</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>17605</t>
+          <t>17150</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>33195</t>
+          <t>32131</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>12903</t>
+          <t>12767</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>27351</t>
+          <t>27811</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>11582</t>
+          <t>11434</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>24690</t>
+          <t>24725</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>27967</t>
+          <t>28145</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>47216</t>
+          <t>47851</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>45990</t>
+          <t>45756</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>69857</t>
+          <t>68118</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>59935</t>
+          <t>58904</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>85267</t>
+          <t>85906</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>112322</t>
+          <t>110758</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>146949</t>
+          <t>146852</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>113114</t>
+          <t>110965</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>146519</t>
+          <t>142447</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>118070</t>
+          <t>117950</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>152635</t>
+          <t>151974</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>239220</t>
+          <t>240880</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>284218</t>
+          <t>285819</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>360889</t>
+          <t>361205</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>398654</t>
+          <t>399542</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>381717</t>
+          <t>381254</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>420920</t>
+          <t>421125</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>757300</t>
+          <t>755629</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>809260</t>
+          <t>809485</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,62%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tomar yogures en 2012 (tasa de respuesta: 99,07%)</t>
+          <t>Menores según la frecuencia de tomar yogures o petit suises en 2012 (tasa de respuesta: 99,07%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>737</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8909</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2351</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10273</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>780</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>6562</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14355</t>
+          <t>13923</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>12316</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11239</t>
+          <t>11809</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9282</t>
+          <t>9163</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20790</t>
+          <t>20507</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17781</t>
+          <t>17521</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7386</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17455</t>
+          <t>17962</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16696</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31571</t>
+          <t>32241</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51116</t>
+          <t>49625</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64677</t>
+          <t>64400</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50170</t>
+          <t>50164</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62786</t>
+          <t>62647</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>105519</t>
+          <t>104541</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>124086</t>
+          <t>124216</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,52%</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>9003</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6447</t>
+          <t>6468</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9760</t>
+          <t>9355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>8992</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4623</t>
+          <t>4505</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13613</t>
+          <t>13698</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19166</t>
+          <t>18845</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>8530</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18192</t>
+          <t>19079</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6474</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16260</t>
+          <t>16957</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17098</t>
+          <t>16633</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31396</t>
+          <t>31502</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57879</t>
+          <t>57989</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71007</t>
+          <t>70371</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56634</t>
+          <t>56360</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70455</t>
+          <t>69840</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>118339</t>
+          <t>117371</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>137695</t>
+          <t>137196</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,68%</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>756</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>743</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12623</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10069</t>
+          <t>9794</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>9291</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6572</t>
+          <t>6523</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17114</t>
+          <t>17452</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14660</t>
+          <t>15382</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14852</t>
+          <t>15711</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13073</t>
+          <t>13004</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27074</t>
+          <t>26727</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>55116</t>
+          <t>54321</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>67141</t>
+          <t>66874</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51827</t>
+          <t>52225</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>64436</t>
+          <t>65190</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111235</t>
+          <t>111392</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>128732</t>
+          <t>129324</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,57%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11974</t>
+          <t>12785</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16665</t>
+          <t>16845</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12703</t>
+          <t>12730</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2232</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10122</t>
+          <t>10352</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20054</t>
+          <t>20079</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>11528</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24816</t>
+          <t>24160</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>11367</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24605</t>
+          <t>24889</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25975</t>
+          <t>25778</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>46056</t>
+          <t>45571</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>14251</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27435</t>
+          <t>28380</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13651</t>
+          <t>13713</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27426</t>
+          <t>27601</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30476</t>
+          <t>30922</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>50494</t>
+          <t>50971</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>123094</t>
+          <t>123636</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>143228</t>
+          <t>142242</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>150388</t>
+          <t>151208</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>170467</t>
+          <t>169476</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>278828</t>
+          <t>277967</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>308430</t>
+          <t>307281</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,49%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>534</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>695</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2359</t>
+          <t>2314</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10118</t>
+          <t>10440</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10898</t>
+          <t>10646</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9190</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17662</t>
+          <t>16766</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7070</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>18649</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8889</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>10333</t>
+          <t>9607</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>22329</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>12914</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26358</t>
+          <t>26689</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12808</t>
+          <t>12814</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>26041</t>
+          <t>25691</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>28969</t>
+          <t>28952</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>48400</t>
+          <t>48128</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>89525</t>
+          <t>89647</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>107056</t>
+          <t>107300</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>90076</t>
+          <t>90380</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>105397</t>
+          <t>106585</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>184464</t>
+          <t>185510</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>208232</t>
+          <t>208263</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,99%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>673</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>10033</t>
+          <t>10281</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7946</t>
+          <t>7802</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>14877</t>
+          <t>15128</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8014</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>11766</t>
+          <t>10821</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5361</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>15780</t>
+          <t>16145</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9602</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>15093</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>9566</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>21197</t>
+          <t>21456</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>26235</t>
+          <t>25856</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>37268</t>
+          <t>36875</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>39091</t>
+          <t>38994</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>51433</t>
+          <t>51299</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>69384</t>
+          <t>68433</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>85948</t>
+          <t>85888</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,65%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>10668</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>25403</t>
+          <t>25032</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>9583</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>21838</t>
+          <t>22490</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>24307</t>
+          <t>24166</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>42733</t>
+          <t>43033</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>22393</t>
+          <t>22120</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>40225</t>
+          <t>39277</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>17326</t>
+          <t>17253</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>32978</t>
+          <t>32972</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>42692</t>
+          <t>43487</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>66675</t>
+          <t>66157</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>40366</t>
+          <t>39548</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>63207</t>
+          <t>61518</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,82 +10073,82 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
+          <t>6,35%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>47300</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>37923</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>59731</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>97447</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>82577</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>113808</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
           <t>6,48%</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>10,14%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>47300</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>36993</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>59143</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>9,08%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>97447</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>83261</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>114720</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>7,65%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>6,53%</t>
-        </is>
-      </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>64972</t>
+          <t>65873</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>92680</t>
+          <t>93275</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>67226</t>
+          <t>66894</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>94639</t>
+          <t>93673</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>139429</t>
+          <t>140434</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>178398</t>
+          <t>177720</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>428371</t>
+          <t>429493</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>464385</t>
+          <t>466983</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>465307</t>
+          <t>466595</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>502052</t>
+          <t>502711</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>906079</t>
+          <t>906440</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>959540</t>
+          <t>956902</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,08%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tomar yogures en 2016 (tasa de respuesta: 98,69%)</t>
+          <t>Menores según la frecuencia de tomar yogures o petit suises en 2016 (tasa de respuesta: 98,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10768,7 +10768,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>716</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10044</t>
+          <t>9475</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13779</t>
+          <t>13956</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15229</t>
+          <t>15086</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12795</t>
+          <t>12599</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25369</t>
+          <t>24924</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14489</t>
+          <t>14455</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26532</t>
+          <t>26300</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16486</t>
+          <t>16282</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30471</t>
+          <t>29859</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33619</t>
+          <t>34154</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52321</t>
+          <t>53058</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33662</t>
+          <t>33265</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47685</t>
+          <t>47679</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44878</t>
+          <t>45057</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59868</t>
+          <t>60349</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>82882</t>
+          <t>82316</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>102838</t>
+          <t>104372</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>63,47%</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>736</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>709</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>613</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5794</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9871</t>
+          <t>9875</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14915</t>
+          <t>14937</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15138</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>12178</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25881</t>
+          <t>25231</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15747</t>
+          <t>16310</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29696</t>
+          <t>29991</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21196</t>
+          <t>19949</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35906</t>
+          <t>35189</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40615</t>
+          <t>41624</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60379</t>
+          <t>61849</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50104</t>
+          <t>49452</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>65374</t>
+          <t>65202</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56450</t>
+          <t>56252</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72745</t>
+          <t>72689</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111254</t>
+          <t>110238</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>133985</t>
+          <t>133063</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>66,82%</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12132,7 +12132,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5653</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>5254</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>7821</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5754</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14889</t>
+          <t>15507</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>12628</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11285</t>
+          <t>11538</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25031</t>
+          <t>24000</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19449</t>
+          <t>19916</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14486</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27629</t>
+          <t>27157</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26486</t>
+          <t>25805</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42293</t>
+          <t>42606</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,81%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22994</t>
+          <t>22745</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34888</t>
+          <t>34971</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33276</t>
+          <t>33232</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47110</t>
+          <t>46736</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>59992</t>
+          <t>60184</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>78352</t>
+          <t>78339</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,16%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2249</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9637</t>
+          <t>9404</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8914</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14685</t>
+          <t>15108</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12292</t>
+          <t>12166</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12828</t>
+          <t>11766</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8315</t>
+          <t>8297</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18622</t>
+          <t>18882</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34657</t>
+          <t>34706</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14164</t>
+          <t>14479</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27775</t>
+          <t>28880</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>37342</t>
+          <t>37322</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>57862</t>
+          <t>58204</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>35408</t>
+          <t>35584</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53575</t>
+          <t>53855</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32992</t>
+          <t>33362</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>54031</t>
+          <t>52645</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>72342</t>
+          <t>74835</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>99524</t>
+          <t>99982</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>112436</t>
+          <t>112067</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>134578</t>
+          <t>135048</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>114674</t>
+          <t>114725</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>137747</t>
+          <t>136736</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>236184</t>
+          <t>235433</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>266873</t>
+          <t>267155</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,69%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>2280</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11505</t>
+          <t>11230</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2443</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>708</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6626</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>13116</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10552</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22682</t>
+          <t>21533</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7925</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>20445</t>
+          <t>19601</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>20988</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>37011</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21155</t>
+          <t>20939</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>36505</t>
+          <t>36576</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>23797</t>
+          <t>24024</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>40568</t>
+          <t>39847</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>49734</t>
+          <t>48969</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>70722</t>
+          <t>71801</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>68339</t>
+          <t>68992</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>87286</t>
+          <t>86666</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>75715</t>
+          <t>75821</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>94404</t>
+          <t>95042</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>149984</t>
+          <t>148084</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>175890</t>
+          <t>175359</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,15%</t>
         </is>
       </c>
     </row>
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>572</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>571</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14248,7 +14248,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6157</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>8513</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11571</t>
+          <t>11490</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>11473</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8191</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>20705</t>
+          <t>19456</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>17239</t>
+          <t>17236</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12949</t>
+          <t>12891</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>25338</t>
+          <t>24535</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>22982</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>39240</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>30557</t>
+          <t>30941</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>42303</t>
+          <t>42344</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>28128</t>
+          <t>28821</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>41205</t>
+          <t>42232</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>62831</t>
+          <t>62882</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>80648</t>
+          <t>80609</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,54%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>21236</t>
+          <t>22935</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>18056</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>17683</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>35446</t>
+          <t>34230</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>17143</t>
+          <t>18175</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>33628</t>
+          <t>32922</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>24859</t>
+          <t>24836</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,7 +15003,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>30944</t>
+          <t>31921</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>52597</t>
+          <t>52862</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>63115</t>
+          <t>62108</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>89674</t>
+          <t>89288</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>53992</t>
+          <t>55239</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>79807</t>
+          <t>80481</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>123894</t>
+          <t>124082</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>160260</t>
+          <t>160535</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>123491</t>
+          <t>123073</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>158089</t>
+          <t>157242</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>146596</t>
+          <t>145379</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>182248</t>
+          <t>181141</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>278846</t>
+          <t>280653</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>331409</t>
+          <t>330852</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>344263</t>
+          <t>345389</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>386059</t>
+          <t>386754</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>384921</t>
+          <t>384333</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>425339</t>
+          <t>427283</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>739662</t>
+          <t>740435</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>799954</t>
+          <t>800326</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,4%</t>
         </is>
       </c>
     </row>
